--- a/VerveStacks_UGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_UGA_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_UGA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0008D47D-6371-40E6-BFE0-B6F5D88A2484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA12CDC7-457A-40CA-9903-4F06E1C03138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1852" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1852" uniqueCount="278">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -618,15 +618,18 @@
     <t>lim_type</t>
   </si>
   <si>
+    <t>e_demand_w171028597-220</t>
+  </si>
+  <si>
+    <t>elc_buildings,elc_transport,elc_industry,elc_roadtransport</t>
+  </si>
+  <si>
+    <t>lo</t>
+  </si>
+  <si>
     <t>e_demand_w212063751-220</t>
   </si>
   <si>
-    <t>elc_buildings,elc_transport,elc_industry,elc_roadtransport</t>
-  </si>
-  <si>
-    <t>lo</t>
-  </si>
-  <si>
     <t>e_demand_w584663033-400</t>
   </si>
   <si>
@@ -648,12 +651,12 @@
     <t>e_demand_w846731380-400</t>
   </si>
   <si>
-    <t>e_demand_UG3-220</t>
-  </si>
-  <si>
     <t>e_demand_UG2-220</t>
   </si>
   <si>
+    <t>ev_battery_w171028597-220</t>
+  </si>
+  <si>
     <t>ev_battery_w212063751-220</t>
   </si>
   <si>
@@ -678,12 +681,12 @@
     <t>ev_battery_w846731380-400</t>
   </si>
   <si>
-    <t>ev_battery_UG3-220</t>
-  </si>
-  <si>
     <t>ev_battery_UG2-220</t>
   </si>
   <si>
+    <t>H2prd_Elc_PEM_w171028597-220</t>
+  </si>
+  <si>
     <t>H2prd_Elc_PEM_w212063751-220</t>
   </si>
   <si>
@@ -708,12 +711,12 @@
     <t>H2prd_Elc_PEM_w846731380-400</t>
   </si>
   <si>
-    <t>H2prd_Elc_PEM_UG3-220</t>
-  </si>
-  <si>
     <t>H2prd_Elc_PEM_UG2-220</t>
   </si>
   <si>
+    <t>H2prd_Elc_ALK_w171028597-220</t>
+  </si>
+  <si>
     <t>H2prd_Elc_ALK_w212063751-220</t>
   </si>
   <si>
@@ -738,9 +741,6 @@
     <t>H2prd_Elc_ALK_w846731380-400</t>
   </si>
   <si>
-    <t>H2prd_Elc_ALK_UG3-220</t>
-  </si>
-  <si>
     <t>H2prd_Elc_ALK_UG2-220</t>
   </si>
   <si>
@@ -750,12 +750,15 @@
     <t>io</t>
   </si>
   <si>
+    <t>e_w171028597-220</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
     <t>e_w212063751-220</t>
   </si>
   <si>
-    <t>IN</t>
-  </si>
-  <si>
     <t>e_w584663033-400</t>
   </si>
   <si>
@@ -777,9 +780,6 @@
     <t>e_w846731380-400</t>
   </si>
   <si>
-    <t>e_UG3-220</t>
-  </si>
-  <si>
     <t>e_UG2-220</t>
   </si>
   <si>
@@ -802,9 +802,6 @@
   </si>
   <si>
     <t>EN_Hydro_UGA-1_w171028597-220</t>
-  </si>
-  <si>
-    <t>e_w171028597-220</t>
   </si>
   <si>
     <t>EN_Hydro_UGA-2_w171028597-220</t>
@@ -1455,7 +1452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47F9C4EB-73D1-4262-A4C2-D9DEB34756CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A2419F-ACF5-4F3D-99CB-39056113F18D}">
   <dimension ref="B2:AF44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1546,7 +1543,7 @@
         <v>164</v>
       </c>
       <c r="J4">
-        <v>0.12566612742428482</v>
+        <v>9.6003678872632302E-3</v>
       </c>
       <c r="K4" t="s">
         <v>165</v>
@@ -1579,19 +1576,19 @@
         <v>160</v>
       </c>
       <c r="AB4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AC4" t="s">
+        <v>272</v>
+      </c>
+      <c r="AD4" t="s">
         <v>273</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>274</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>275</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.45">
@@ -1614,7 +1611,7 @@
         <v>164</v>
       </c>
       <c r="J5">
-        <v>0.31017182235318741</v>
+        <v>0.12685140641584375</v>
       </c>
       <c r="K5" t="s">
         <v>165</v>
@@ -1644,10 +1641,10 @@
         <v>221</v>
       </c>
       <c r="AA5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AB5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -1656,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.45">
@@ -1679,7 +1676,7 @@
         <v>164</v>
       </c>
       <c r="J6">
-        <v>4.5588304883418536E-2</v>
+        <v>0.31309735330050081</v>
       </c>
       <c r="K6" t="s">
         <v>165</v>
@@ -1709,10 +1706,10 @@
         <v>221</v>
       </c>
       <c r="AA6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AB6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AD6">
         <v>2</v>
@@ -1721,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.45">
@@ -1744,7 +1741,7 @@
         <v>164</v>
       </c>
       <c r="J7">
-        <v>0.10242788201259054</v>
+        <v>4.6018292352171003E-2</v>
       </c>
       <c r="K7" t="s">
         <v>165</v>
@@ -1768,7 +1765,7 @@
         <v>224</v>
       </c>
       <c r="W7" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="X7" t="s">
         <v>221</v>
@@ -1794,7 +1791,7 @@
         <v>164</v>
       </c>
       <c r="J8">
-        <v>9.726382747665839E-2</v>
+        <v>0.10339397859874132</v>
       </c>
       <c r="K8" t="s">
         <v>165</v>
@@ -1815,10 +1812,10 @@
         <v>118</v>
       </c>
       <c r="V8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="W8" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="X8" t="s">
         <v>221</v>
@@ -1844,7 +1841,7 @@
         <v>164</v>
       </c>
       <c r="J9">
-        <v>0.10756481936716944</v>
+        <v>9.8181216861607495E-2</v>
       </c>
       <c r="K9" t="s">
         <v>165</v>
@@ -1865,10 +1862,10 @@
         <v>118</v>
       </c>
       <c r="V9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="W9" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="X9" t="s">
         <v>221</v>
@@ -1894,7 +1891,7 @@
         <v>164</v>
       </c>
       <c r="J10">
-        <v>5.588693875815981E-2</v>
+        <v>0.10857936738611403</v>
       </c>
       <c r="K10" t="s">
         <v>165</v>
@@ -1915,10 +1912,10 @@
         <v>118</v>
       </c>
       <c r="V10" t="s">
+        <v>227</v>
+      </c>
+      <c r="W10" t="s">
         <v>228</v>
-      </c>
-      <c r="W10" t="s">
-        <v>229</v>
       </c>
       <c r="X10" t="s">
         <v>221</v>
@@ -1944,7 +1941,7 @@
         <v>164</v>
       </c>
       <c r="J11">
-        <v>6.4609632093396596E-2</v>
+        <v>5.6414062620176626E-2</v>
       </c>
       <c r="K11" t="s">
         <v>165</v>
@@ -1965,10 +1962,10 @@
         <v>118</v>
       </c>
       <c r="V11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X11" t="s">
         <v>221</v>
@@ -1994,7 +1991,7 @@
         <v>164</v>
       </c>
       <c r="J12">
-        <v>1.8667624844503294E-2</v>
+        <v>6.5219028126697567E-2</v>
       </c>
       <c r="K12" t="s">
         <v>165</v>
@@ -2015,10 +2012,10 @@
         <v>118</v>
       </c>
       <c r="V12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="W12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X12" t="s">
         <v>221</v>
@@ -2044,7 +2041,7 @@
         <v>164</v>
       </c>
       <c r="J13">
-        <v>5.2153020786630831E-2</v>
+        <v>5.2644926450883631E-2</v>
       </c>
       <c r="K13" t="s">
         <v>165</v>
@@ -2065,10 +2062,10 @@
         <v>118</v>
       </c>
       <c r="V13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="W13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="X13" t="s">
         <v>221</v>
@@ -2094,7 +2091,7 @@
         <v>164</v>
       </c>
       <c r="J14">
-        <v>0.12566612742428482</v>
+        <v>9.6003678872632302E-3</v>
       </c>
       <c r="K14" t="s">
         <v>165</v>
@@ -2115,10 +2112,10 @@
         <v>118</v>
       </c>
       <c r="V14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="X14" t="s">
         <v>221</v>
@@ -2144,7 +2141,7 @@
         <v>164</v>
       </c>
       <c r="J15">
-        <v>0.31017182235318741</v>
+        <v>0.12685140641584375</v>
       </c>
       <c r="K15" t="s">
         <v>165</v>
@@ -2165,10 +2162,10 @@
         <v>118</v>
       </c>
       <c r="V15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="X15" t="s">
         <v>221</v>
@@ -2194,7 +2191,7 @@
         <v>164</v>
       </c>
       <c r="J16">
-        <v>4.5588304883418536E-2</v>
+        <v>0.31309735330050081</v>
       </c>
       <c r="K16" t="s">
         <v>165</v>
@@ -2215,10 +2212,10 @@
         <v>118</v>
       </c>
       <c r="V16" t="s">
+        <v>234</v>
+      </c>
+      <c r="W16" t="s">
         <v>235</v>
-      </c>
-      <c r="W16" t="s">
-        <v>236</v>
       </c>
       <c r="X16" t="s">
         <v>221</v>
@@ -2244,7 +2241,7 @@
         <v>164</v>
       </c>
       <c r="J17">
-        <v>0.10242788201259054</v>
+        <v>4.6018292352171003E-2</v>
       </c>
       <c r="K17" t="s">
         <v>165</v>
@@ -2265,10 +2262,10 @@
         <v>118</v>
       </c>
       <c r="V17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="W17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X17" t="s">
         <v>221</v>
@@ -2294,7 +2291,7 @@
         <v>164</v>
       </c>
       <c r="J18">
-        <v>9.726382747665839E-2</v>
+        <v>0.10339397859874132</v>
       </c>
       <c r="K18" t="s">
         <v>165</v>
@@ -2315,10 +2312,10 @@
         <v>118</v>
       </c>
       <c r="V18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="W18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X18" t="s">
         <v>221</v>
@@ -2344,7 +2341,7 @@
         <v>164</v>
       </c>
       <c r="J19">
-        <v>0.10756481936716944</v>
+        <v>9.8181216861607495E-2</v>
       </c>
       <c r="K19" t="s">
         <v>165</v>
@@ -2365,10 +2362,10 @@
         <v>118</v>
       </c>
       <c r="V19" t="s">
+        <v>238</v>
+      </c>
+      <c r="W19" t="s">
         <v>239</v>
-      </c>
-      <c r="W19" t="s">
-        <v>240</v>
       </c>
       <c r="X19" t="s">
         <v>221</v>
@@ -2394,7 +2391,7 @@
         <v>164</v>
       </c>
       <c r="J20">
-        <v>5.588693875815981E-2</v>
+        <v>0.10857936738611403</v>
       </c>
       <c r="K20" t="s">
         <v>165</v>
@@ -2415,10 +2412,10 @@
         <v>118</v>
       </c>
       <c r="V20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="X20" t="s">
         <v>221</v>
@@ -2444,7 +2441,7 @@
         <v>164</v>
       </c>
       <c r="J21">
-        <v>6.4609632093396596E-2</v>
+        <v>5.6414062620176626E-2</v>
       </c>
       <c r="K21" t="s">
         <v>165</v>
@@ -2465,10 +2462,10 @@
         <v>118</v>
       </c>
       <c r="V21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="X21" t="s">
         <v>221</v>
@@ -2494,7 +2491,7 @@
         <v>164</v>
       </c>
       <c r="J22">
-        <v>1.8667624844503294E-2</v>
+        <v>6.5219028126697567E-2</v>
       </c>
       <c r="K22" t="s">
         <v>165</v>
@@ -2515,10 +2512,10 @@
         <v>118</v>
       </c>
       <c r="V22" t="s">
+        <v>242</v>
+      </c>
+      <c r="W22" t="s">
         <v>243</v>
-      </c>
-      <c r="W22" t="s">
-        <v>244</v>
       </c>
       <c r="X22" t="s">
         <v>221</v>
@@ -2544,7 +2541,7 @@
         <v>164</v>
       </c>
       <c r="J23">
-        <v>5.2153020786630831E-2</v>
+        <v>5.2644926450883631E-2</v>
       </c>
       <c r="K23" t="s">
         <v>165</v>
@@ -2565,10 +2562,10 @@
         <v>118</v>
       </c>
       <c r="V23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="W23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X23" t="s">
         <v>221</v>
@@ -2594,7 +2591,7 @@
         <v>164</v>
       </c>
       <c r="J24">
-        <v>0.12566612742428482</v>
+        <v>9.6003678872632302E-3</v>
       </c>
       <c r="K24" t="s">
         <v>165</v>
@@ -2615,10 +2612,10 @@
         <v>118</v>
       </c>
       <c r="V24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="W24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X24" t="s">
         <v>221</v>
@@ -2644,7 +2641,7 @@
         <v>164</v>
       </c>
       <c r="J25">
-        <v>0.31017182235318741</v>
+        <v>0.12685140641584375</v>
       </c>
       <c r="K25" t="s">
         <v>165</v>
@@ -2665,10 +2662,10 @@
         <v>118</v>
       </c>
       <c r="V25" t="s">
+        <v>246</v>
+      </c>
+      <c r="W25" t="s">
         <v>247</v>
-      </c>
-      <c r="W25" t="s">
-        <v>248</v>
       </c>
       <c r="X25" t="s">
         <v>221</v>
@@ -2694,7 +2691,7 @@
         <v>164</v>
       </c>
       <c r="J26">
-        <v>4.5588304883418536E-2</v>
+        <v>0.31309735330050081</v>
       </c>
       <c r="K26" t="s">
         <v>165</v>
@@ -2715,10 +2712,10 @@
         <v>118</v>
       </c>
       <c r="V26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="W26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="X26" t="s">
         <v>221</v>
@@ -2744,7 +2741,7 @@
         <v>164</v>
       </c>
       <c r="J27">
-        <v>0.10242788201259054</v>
+        <v>4.6018292352171003E-2</v>
       </c>
       <c r="K27" t="s">
         <v>165</v>
@@ -2765,10 +2762,10 @@
         <v>118</v>
       </c>
       <c r="V27" t="s">
+        <v>249</v>
+      </c>
+      <c r="W27" t="s">
         <v>250</v>
-      </c>
-      <c r="W27" t="s">
-        <v>251</v>
       </c>
       <c r="X27" t="s">
         <v>221</v>
@@ -2794,7 +2791,7 @@
         <v>164</v>
       </c>
       <c r="J28">
-        <v>9.726382747665839E-2</v>
+        <v>0.10339397859874132</v>
       </c>
       <c r="K28" t="s">
         <v>165</v>
@@ -2815,10 +2812,10 @@
         <v>118</v>
       </c>
       <c r="V28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="W28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="X28" t="s">
         <v>221</v>
@@ -2844,7 +2841,7 @@
         <v>164</v>
       </c>
       <c r="J29">
-        <v>0.10756481936716944</v>
+        <v>9.8181216861607495E-2</v>
       </c>
       <c r="K29" t="s">
         <v>165</v>
@@ -2865,10 +2862,10 @@
         <v>118</v>
       </c>
       <c r="V29" t="s">
+        <v>252</v>
+      </c>
+      <c r="W29" t="s">
         <v>253</v>
-      </c>
-      <c r="W29" t="s">
-        <v>254</v>
       </c>
       <c r="X29" t="s">
         <v>221</v>
@@ -2894,7 +2891,7 @@
         <v>164</v>
       </c>
       <c r="J30">
-        <v>5.588693875815981E-2</v>
+        <v>0.10857936738611403</v>
       </c>
       <c r="K30" t="s">
         <v>165</v>
@@ -2915,10 +2912,10 @@
         <v>118</v>
       </c>
       <c r="V30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="W30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="X30" t="s">
         <v>221</v>
@@ -2944,7 +2941,7 @@
         <v>164</v>
       </c>
       <c r="J31">
-        <v>6.4609632093396596E-2</v>
+        <v>5.6414062620176626E-2</v>
       </c>
       <c r="K31" t="s">
         <v>165</v>
@@ -2965,7 +2962,7 @@
         <v>118</v>
       </c>
       <c r="V31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="W31" t="s">
         <v>220</v>
@@ -2994,7 +2991,7 @@
         <v>164</v>
       </c>
       <c r="J32">
-        <v>1.8667624844503294E-2</v>
+        <v>6.5219028126697567E-2</v>
       </c>
       <c r="K32" t="s">
         <v>165</v>
@@ -3015,7 +3012,7 @@
         <v>118</v>
       </c>
       <c r="V32" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="W32" t="s">
         <v>220</v>
@@ -3044,7 +3041,7 @@
         <v>164</v>
       </c>
       <c r="J33">
-        <v>5.2153020786630831E-2</v>
+        <v>5.2644926450883631E-2</v>
       </c>
       <c r="K33" t="s">
         <v>165</v>
@@ -3065,10 +3062,10 @@
         <v>118</v>
       </c>
       <c r="V33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W33" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="X33" t="s">
         <v>221</v>
@@ -3094,7 +3091,7 @@
         <v>164</v>
       </c>
       <c r="J34">
-        <v>0.12566612742428482</v>
+        <v>9.6003678872632302E-3</v>
       </c>
       <c r="K34" t="s">
         <v>165</v>
@@ -3115,10 +3112,10 @@
         <v>118</v>
       </c>
       <c r="V34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="W34" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="X34" t="s">
         <v>221</v>
@@ -3144,7 +3141,7 @@
         <v>164</v>
       </c>
       <c r="J35">
-        <v>0.31017182235318741</v>
+        <v>0.12685140641584375</v>
       </c>
       <c r="K35" t="s">
         <v>165</v>
@@ -3165,10 +3162,10 @@
         <v>118</v>
       </c>
       <c r="V35" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X35" t="s">
         <v>221</v>
@@ -3194,7 +3191,7 @@
         <v>164</v>
       </c>
       <c r="J36">
-        <v>4.5588304883418536E-2</v>
+        <v>0.31309735330050081</v>
       </c>
       <c r="K36" t="s">
         <v>165</v>
@@ -3215,10 +3212,10 @@
         <v>118</v>
       </c>
       <c r="V36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="W36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="X36" t="s">
         <v>221</v>
@@ -3244,7 +3241,7 @@
         <v>164</v>
       </c>
       <c r="J37">
-        <v>0.10242788201259054</v>
+        <v>4.6018292352171003E-2</v>
       </c>
       <c r="K37" t="s">
         <v>165</v>
@@ -3265,10 +3262,10 @@
         <v>118</v>
       </c>
       <c r="V37" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W37" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="X37" t="s">
         <v>221</v>
@@ -3294,7 +3291,7 @@
         <v>164</v>
       </c>
       <c r="J38">
-        <v>9.726382747665839E-2</v>
+        <v>0.10339397859874132</v>
       </c>
       <c r="K38" t="s">
         <v>165</v>
@@ -3315,10 +3312,10 @@
         <v>118</v>
       </c>
       <c r="V38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="W38" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="X38" t="s">
         <v>221</v>
@@ -3344,7 +3341,7 @@
         <v>164</v>
       </c>
       <c r="J39">
-        <v>0.10756481936716944</v>
+        <v>9.8181216861607495E-2</v>
       </c>
       <c r="K39" t="s">
         <v>165</v>
@@ -3365,10 +3362,10 @@
         <v>118</v>
       </c>
       <c r="V39" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="W39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X39" t="s">
         <v>221</v>
@@ -3394,7 +3391,7 @@
         <v>164</v>
       </c>
       <c r="J40">
-        <v>5.588693875815981E-2</v>
+        <v>0.10857936738611403</v>
       </c>
       <c r="K40" t="s">
         <v>165</v>
@@ -3415,10 +3412,10 @@
         <v>118</v>
       </c>
       <c r="V40" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="W40" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X40" t="s">
         <v>221</v>
@@ -3432,7 +3429,7 @@
         <v>164</v>
       </c>
       <c r="J41">
-        <v>6.4609632093396596E-2</v>
+        <v>5.6414062620176626E-2</v>
       </c>
       <c r="K41" t="s">
         <v>165</v>
@@ -3453,10 +3450,10 @@
         <v>118</v>
       </c>
       <c r="V41" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="W41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="X41" t="s">
         <v>221</v>
@@ -3470,7 +3467,7 @@
         <v>164</v>
       </c>
       <c r="J42">
-        <v>1.8667624844503294E-2</v>
+        <v>6.5219028126697567E-2</v>
       </c>
       <c r="K42" t="s">
         <v>165</v>
@@ -3491,10 +3488,10 @@
         <v>118</v>
       </c>
       <c r="V42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="W42" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="X42" t="s">
         <v>221</v>
@@ -3508,7 +3505,7 @@
         <v>164</v>
       </c>
       <c r="J43">
-        <v>5.2153020786630831E-2</v>
+        <v>5.2644926450883631E-2</v>
       </c>
       <c r="K43" t="s">
         <v>165</v>
@@ -3529,10 +3526,10 @@
         <v>118</v>
       </c>
       <c r="V43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="W43" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X43" t="s">
         <v>221</v>
@@ -3543,10 +3540,10 @@
         <v>118</v>
       </c>
       <c r="V44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="W44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X44" t="s">
         <v>221</v>
@@ -3558,7 +3555,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7406AE3A-4C2B-4888-AA25-391643E209DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2E2A0A-02E1-4C70-98EE-3797A51F136B}">
   <dimension ref="B9:L17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
